--- a/EXCEL/Exercise Files/Chapter04/04_03_Exponential.xlsx
+++ b/EXCEL/Exercise Files/Chapter04/04_03_Exponential.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter04\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter04\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A899910-B1AE-456E-BA92-AFD900151E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908FEBEF-6220-41C0-A7D2-298C4E366769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -280,79 +289,79 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="25"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>0.16374615061559639</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>0.13406400920712788</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>0.10976232721880529</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>8.9865792823444313E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>7.357588823428847E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>6.0238842382440407E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>4.9319392788321287E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0</c:v>
+                  <c:v>4.0379303598931077E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>3.3059777644317306E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>2.7067056647322542E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>2.2160631672466777E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0</c:v>
+                  <c:v>1.8143590657882496E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v>1.4854715642866776E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v>1.2162012525043592E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>9.9574136735727896E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>8.152440795673243E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0</c:v>
+                  <c:v>6.6746539920652138E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0</c:v>
+                  <c:v>5.4647444894585125E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>4.4741543712331182E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0</c:v>
+                  <c:v>3.6631277777468361E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>2.9991153640955407E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0</c:v>
+                  <c:v>2.4554679806136873E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0</c:v>
+                  <c:v>2.010367148926715E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0</c:v>
+                  <c:v>1.6459494098040048E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0</c:v>
+                  <c:v>1.3475893998170934E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1405,14 +1414,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.69140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,210 +1436,236 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+        <f>_xlfn.EXPON.DIST(A2,1/$E$1,FALSE)</f>
+        <v>0.16374615061559639</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <f t="shared" ref="B3:B26" si="0">_xlfn.EXPON.DIST(A3,1/$E$1,FALSE)</f>
+        <v>0.13406400920712788</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+        <f>_xlfn.EXPON.DIST(7,1/E1,TRUE)-_xlfn.EXPON.DIST(3,1/E1,TRUE)</f>
+        <v>0.30221467215241998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>0.10976232721880529</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>8.9865792823444313E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>7.357588823428847E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>6.0238842382440407E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>4.9319392788321287E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>4.0379303598931077E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>3.3059777644317306E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.7067056647322542E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.2160631672466777E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>1.8143590657882496E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>1.4854715642866776E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>1.2162012525043592E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>9.9574136735727896E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>8.152440795673243E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>6.6746539920652138E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>5.4647444894585125E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>4.4741543712331182E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>3.6631277777468361E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.9991153640955407E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.4554679806136873E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>2.010367148926715E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>1.6459494098040048E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1.3475893998170934E-3</v>
       </c>
     </row>
   </sheetData>
